--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750083438_h_2.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01191505233618673</v>
+        <v>0.00469032674960822</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008402787308176896</v>
+        <v>0.008402251151435237</v>
       </c>
       <c r="C2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>9514310</v>
+        <v>4835653</v>
       </c>
       <c r="L2" t="n">
-        <v>5730410</v>
+        <v>2968564</v>
       </c>
       <c r="M2" t="n">
-        <v>1497989</v>
+        <v>784528</v>
       </c>
       <c r="N2" t="n">
-        <v>94233</v>
+        <v>46265</v>
       </c>
       <c r="O2" t="n">
-        <v>877922</v>
+        <v>458794</v>
       </c>
       <c r="P2" t="n">
-        <v>348088</v>
+        <v>179404</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999867081642151</v>
+        <v>0.9999858140945435</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9365760684013367</v>
+        <v>0.9526019096374512</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8652430176734924</v>
+        <v>0.898713231086731</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8082126379013062</v>
+        <v>0.8516222238540649</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6245559453964233</v>
+        <v>0.70071941614151</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8603476881980896</v>
+        <v>0.8993210196495056</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9022428393363953</v>
+        <v>0.930769681930542</v>
       </c>
       <c r="X2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12726162</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>9738416</v>
+        <v>4854570</v>
       </c>
       <c r="AG2" t="n">
-        <v>5978550</v>
+        <v>2980268</v>
       </c>
       <c r="AH2" t="n">
-        <v>1603341</v>
+        <v>800821</v>
       </c>
       <c r="AI2" t="n">
-        <v>118358</v>
+        <v>59096</v>
       </c>
       <c r="AJ2" t="n">
-        <v>918488</v>
+        <v>459081</v>
       </c>
       <c r="AK2" t="n">
-        <v>360037</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.956718921661377</v>
+        <v>0.9567334651947021</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911195695400238</v>
+        <v>0.9111363887786865</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580697178840637</v>
+        <v>0.8581864833831787</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.662520706653595</v>
+        <v>0.6625929474830627</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901969313621521</v>
+        <v>0.9019822478294373</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314232468605042</v>
+        <v>0.931419849395752</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002805756907194128</v>
+        <v>0.001042420015018964</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002013083763574795</v>
+        <v>0.002013410135496696</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>9514310</v>
+        <v>4835653</v>
       </c>
       <c r="E3" t="n">
-        <v>625304</v>
+        <v>225121</v>
       </c>
       <c r="F3" t="n">
-        <v>21056</v>
+        <v>7316</v>
       </c>
       <c r="G3" t="n">
-        <v>7662</v>
+        <v>1039</v>
       </c>
       <c r="H3" t="n">
-        <v>528</v>
+        <v>154</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>20192069</v>
+        <v>10069530</v>
       </c>
       <c r="K3" t="n">
-        <v>22105173</v>
+        <v>11106088</v>
       </c>
       <c r="L3" t="n">
-        <v>25456327</v>
+        <v>12806574</v>
       </c>
       <c r="M3" t="n">
-        <v>30693354</v>
+        <v>15345602</v>
       </c>
       <c r="N3" t="n">
-        <v>32682970</v>
+        <v>16306975</v>
       </c>
       <c r="O3" t="n">
-        <v>31757119</v>
+        <v>15855445</v>
       </c>
       <c r="P3" t="n">
-        <v>32494102</v>
+        <v>16209374</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9356256723403931</v>
+        <v>0.9539080858230591</v>
       </c>
       <c r="S3" t="n">
-        <v>0.872262716293335</v>
+        <v>0.9064697027206421</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8012453317642212</v>
+        <v>0.8402266502380371</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5270802974700928</v>
+        <v>0.518288254737854</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8617419600486755</v>
+        <v>0.9010218381881714</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9004223942756653</v>
+        <v>0.9281981587409973</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9738416</v>
+        <v>4854570</v>
       </c>
       <c r="Z3" t="n">
-        <v>399532</v>
+        <v>199283</v>
       </c>
       <c r="AA3" t="n">
-        <v>17188</v>
+        <v>8572</v>
       </c>
       <c r="AB3" t="n">
-        <v>13642</v>
+        <v>6807</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>20192238</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>22308915</v>
+        <v>11127154</v>
       </c>
       <c r="AG3" t="n">
-        <v>25766144</v>
+        <v>12850470</v>
       </c>
       <c r="AH3" t="n">
-        <v>30783621</v>
+        <v>15349956</v>
       </c>
       <c r="AI3" t="n">
-        <v>32679327</v>
+        <v>16296642</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31799798</v>
+        <v>15856919</v>
       </c>
       <c r="AK3" t="n">
-        <v>32505309</v>
+        <v>16209464</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576639533042908</v>
+        <v>0.957639753818512</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100337028503418</v>
+        <v>0.9100435376167297</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575960397720337</v>
+        <v>0.8576763868331909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6620204448699951</v>
+        <v>0.6620287895202637</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015603065490723</v>
+        <v>0.9015854597091675</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313316941261292</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03946237817998225</v>
+        <v>0.01897579137883037</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03182118993392174</v>
+        <v>0.03181825301110282</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>607950</v>
+        <v>225611</v>
       </c>
       <c r="E4" t="n">
-        <v>5730410</v>
+        <v>2968564</v>
       </c>
       <c r="F4" t="n">
-        <v>215433</v>
+        <v>77828</v>
       </c>
       <c r="G4" t="n">
-        <v>8095</v>
+        <v>1630</v>
       </c>
       <c r="H4" t="n">
-        <v>7255</v>
+        <v>1170</v>
       </c>
       <c r="I4" t="n">
-        <v>442</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="K4" t="n">
-        <v>644299</v>
+        <v>240605</v>
       </c>
       <c r="L4" t="n">
-        <v>892481</v>
+        <v>334563</v>
       </c>
       <c r="M4" t="n">
-        <v>355470</v>
+        <v>136688</v>
       </c>
       <c r="N4" t="n">
-        <v>56647</v>
+        <v>19760</v>
       </c>
       <c r="O4" t="n">
-        <v>142505</v>
+        <v>51362</v>
       </c>
       <c r="P4" t="n">
-        <v>37715</v>
+        <v>13344</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999933838844299</v>
+        <v>0.9999929070472717</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9361006617546082</v>
+        <v>0.9532545804977417</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8687387108802795</v>
+        <v>0.9025747776031494</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8047139644622803</v>
+        <v>0.8458860516548157</v>
       </c>
       <c r="U4" t="n">
-        <v>0.571692943572998</v>
+        <v>0.5958529114723206</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8610442280769348</v>
+        <v>0.900170624256134</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9013317227363586</v>
+        <v>0.9294821619987488</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>411369</v>
+        <v>204986</v>
       </c>
       <c r="Z4" t="n">
-        <v>5978550</v>
+        <v>2980268</v>
       </c>
       <c r="AA4" t="n">
-        <v>166219</v>
+        <v>82895</v>
       </c>
       <c r="AB4" t="n">
-        <v>11022</v>
+        <v>5498</v>
       </c>
       <c r="AC4" t="n">
-        <v>2296</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>440557</v>
+        <v>219539</v>
       </c>
       <c r="AG4" t="n">
-        <v>582664</v>
+        <v>290667</v>
       </c>
       <c r="AH4" t="n">
-        <v>265203</v>
+        <v>132334</v>
       </c>
       <c r="AI4" t="n">
-        <v>60290</v>
+        <v>30093</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99826</v>
+        <v>49888</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571911692619324</v>
+        <v>0.9571864008903503</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106143116950989</v>
+        <v>0.9105896949768066</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578327894210815</v>
+        <v>0.8579313158988953</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622704863548279</v>
+        <v>0.662310779094696</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017647504806519</v>
+        <v>0.90178382396698</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313774704933167</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>20934</v>
+        <v>8696</v>
       </c>
       <c r="E5" t="n">
-        <v>243938</v>
+        <v>101529</v>
       </c>
       <c r="F5" t="n">
-        <v>1497989</v>
+        <v>784528</v>
       </c>
       <c r="G5" t="n">
-        <v>22339</v>
+        <v>9127</v>
       </c>
       <c r="H5" t="n">
-        <v>81292</v>
+        <v>29206</v>
       </c>
       <c r="I5" t="n">
-        <v>3081</v>
+        <v>623</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>654618</v>
+        <v>233654</v>
       </c>
       <c r="L5" t="n">
-        <v>839182</v>
+        <v>306299</v>
       </c>
       <c r="M5" t="n">
-        <v>371587</v>
+        <v>149182</v>
       </c>
       <c r="N5" t="n">
-        <v>84550</v>
+        <v>43000</v>
       </c>
       <c r="O5" t="n">
-        <v>140854</v>
+        <v>50399</v>
       </c>
       <c r="P5" t="n">
-        <v>38495</v>
+        <v>13878</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999948740005493</v>
+        <v>0.9999945163726807</v>
       </c>
       <c r="R5" t="n">
-        <v>0.960541307926178</v>
+        <v>0.971109926700592</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9473952651023865</v>
+        <v>0.9609611630439758</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9779133796691895</v>
+        <v>0.9825859069824219</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9957106709480286</v>
+        <v>0.9961768984794617</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9913920760154724</v>
+        <v>0.9938011169433594</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976848959922791</v>
+        <v>0.9983417391777039</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>16114</v>
+        <v>8031</v>
       </c>
       <c r="Z5" t="n">
-        <v>170607</v>
+        <v>85136</v>
       </c>
       <c r="AA5" t="n">
-        <v>1603341</v>
+        <v>800821</v>
       </c>
       <c r="AB5" t="n">
-        <v>19925</v>
+        <v>9950</v>
       </c>
       <c r="AC5" t="n">
-        <v>58323</v>
+        <v>29139</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>430512</v>
+        <v>214737</v>
       </c>
       <c r="AG5" t="n">
-        <v>591042</v>
+        <v>294595</v>
       </c>
       <c r="AH5" t="n">
-        <v>266235</v>
+        <v>132889</v>
       </c>
       <c r="AI5" t="n">
-        <v>60425</v>
+        <v>30169</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100288</v>
+        <v>50112</v>
       </c>
       <c r="AK5" t="n">
-        <v>26546</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735385179519653</v>
+        <v>0.9735455513000488</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643449783325195</v>
+        <v>0.9643480777740479</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838559031486511</v>
+        <v>0.9838436245918274</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963328838348389</v>
+        <v>0.9963290691375732</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939209222793579</v>
+        <v>0.9939084053039551</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983882904052734</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>15333</v>
+        <v>6259</v>
       </c>
       <c r="E6" t="n">
-        <v>16834</v>
+        <v>7006</v>
       </c>
       <c r="F6" t="n">
-        <v>33319</v>
+        <v>21549</v>
       </c>
       <c r="G6" t="n">
-        <v>94233</v>
+        <v>46265</v>
       </c>
       <c r="H6" t="n">
-        <v>17678</v>
+        <v>7676</v>
       </c>
       <c r="I6" t="n">
-        <v>1365</v>
+        <v>503</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12962</v>
+        <v>6466</v>
       </c>
       <c r="Z6" t="n">
-        <v>10739</v>
+        <v>5355</v>
       </c>
       <c r="AA6" t="n">
-        <v>21783</v>
+        <v>10880</v>
       </c>
       <c r="AB6" t="n">
-        <v>118358</v>
+        <v>59096</v>
       </c>
       <c r="AC6" t="n">
-        <v>13979</v>
+        <v>6987</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E7" t="n">
-        <v>6048</v>
+        <v>811</v>
       </c>
       <c r="F7" t="n">
-        <v>84117</v>
+        <v>29660</v>
       </c>
       <c r="G7" t="n">
-        <v>17833</v>
+        <v>7738</v>
       </c>
       <c r="H7" t="n">
-        <v>877922</v>
+        <v>458794</v>
       </c>
       <c r="I7" t="n">
-        <v>32762</v>
+        <v>12138</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1624</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>59353</v>
+        <v>29657</v>
       </c>
       <c r="AB7" t="n">
-        <v>15171</v>
+        <v>7573</v>
       </c>
       <c r="AC7" t="n">
-        <v>918488</v>
+        <v>459081</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E8" t="n">
-        <v>357</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>1545</v>
+        <v>335</v>
       </c>
       <c r="G8" t="n">
-        <v>718</v>
+        <v>226</v>
       </c>
       <c r="H8" t="n">
-        <v>35752</v>
+        <v>13156</v>
       </c>
       <c r="I8" t="n">
-        <v>348088</v>
+        <v>179404</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25138</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360037</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
